--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,85 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
+    <t>PARRA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
+    <t>FLORES</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
+    <t>SUEMI</t>
   </si>
   <si>
     <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
   </si>
 </sst>
 </file>
@@ -555,19 +492,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>52.78</v>
+        <v>63.89</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -607,19 +544,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>88.89</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -633,19 +570,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>48.48</v>
+        <v>63.64</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -698,16 +635,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>38.89</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -721,16 +661,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>64.09999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -744,16 +687,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>61.11</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -767,16 +713,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -829,19 +778,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>52.78</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -858,16 +807,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -881,19 +830,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>88.89</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -907,19 +856,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>48.48</v>
+        <v>63.64</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -929,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -961,39 +910,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920072</v>
+        <v>20330051920306</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920073</v>
+        <v>20330051920082</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1002,191 +951,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920081</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920082</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920070</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920162</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920009</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920090</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920226</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920306</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
@@ -951,7 +951,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,22 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PARRA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>SUEMI</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -713,19 +704,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>33.33</v>
+        <v>51.52</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -859,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>63.64</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -878,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -910,47 +901,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920306</v>
+        <v>20330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920082</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
         <v>3</v>
       </c>
     </row>

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
@@ -626,19 +626,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>38.89</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -652,19 +652,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>64.09999999999999</v>
+        <v>69.23</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -678,16 +678,16 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
         <v>8.1</v>
@@ -704,19 +704,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>51.52</v>
+        <v>54.55</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -772,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -798,16 +798,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>89.73999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
+++ b/docentes/Rivera Cruz Ezequiel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
+    <t>NICIO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>PARRA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JOSE JULIAN</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>SUEMI</t>
   </si>
 </sst>
 </file>
@@ -626,19 +680,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>69.44</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -652,19 +706,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>69.23</v>
+        <v>94.87</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -678,19 +732,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -704,19 +758,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>54.55</v>
+        <v>66.67</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -772,16 +826,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>77.78</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -798,16 +852,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>94.87</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -824,16 +878,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>86.11</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -850,16 +904,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>75.76000000000001</v>
+        <v>51.52</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +923,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,16 +955,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920003</v>
+        <v>20330051920025</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -919,7 +973,145 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920074</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920051</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920065</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920082</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920062</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920306</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
